--- a/AtchisonRegime/Outputs/Euro/MSCI_Europe/df_regSettingsMSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/Euro/MSCI_Europe/df_regSettingsMSCI_Europe.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I316"/>
+  <dimension ref="A1:I317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10521,7 +10521,7 @@
         <v>-1.173508054480522</v>
       </c>
       <c r="C306" t="n">
-        <v>0.07440878746934976</v>
+        <v>0.003059559528599793</v>
       </c>
       <c r="D306" t="b">
         <v>0</v>
@@ -10554,7 +10554,7 @@
         <v>-1.176877030846902</v>
       </c>
       <c r="C307" t="n">
-        <v>0.0780392389232072</v>
+        <v>0.06963252061712617</v>
       </c>
       <c r="D307" t="b">
         <v>0</v>
@@ -10587,7 +10587,7 @@
         <v>-1.162274350584444</v>
       </c>
       <c r="C308" t="n">
-        <v>0.07326265395948543</v>
+        <v>0.06271089526937522</v>
       </c>
       <c r="D308" t="b">
         <v>0</v>
@@ -10620,7 +10620,7 @@
         <v>-1.192124318497693</v>
       </c>
       <c r="C309" t="n">
-        <v>0.05790582692168544</v>
+        <v>0.04690694013080018</v>
       </c>
       <c r="D309" t="b">
         <v>0</v>
@@ -10653,7 +10653,7 @@
         <v>-1.247901006063838</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.05170998467301801</v>
+        <v>0.03049422547834524</v>
       </c>
       <c r="D310" t="b">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>-1.274041300528749</v>
       </c>
       <c r="C311" t="n">
-        <v>0.01934764035298829</v>
+        <v>0.02255665395177126</v>
       </c>
       <c r="D311" t="b">
         <v>0</v>
@@ -10719,7 +10719,7 @@
         <v>-1.224213763458834</v>
       </c>
       <c r="C312" t="n">
-        <v>0.03207639871494124</v>
+        <v>0.02775436740155613</v>
       </c>
       <c r="D312" t="b">
         <v>0</v>
@@ -10752,7 +10752,7 @@
         <v>-1.100583367531713</v>
       </c>
       <c r="C313" t="n">
-        <v>0.04710340453708419</v>
+        <v>0.04565116666107294</v>
       </c>
       <c r="D313" t="b">
         <v>0</v>
@@ -10785,7 +10785,7 @@
         <v>-1.004917433510945</v>
       </c>
       <c r="C314" t="n">
-        <v>0.08885128292497106</v>
+        <v>0.07696715706128913</v>
       </c>
       <c r="D314" t="b">
         <v>0</v>
@@ -10815,10 +10815,10 @@
         <v>45716</v>
       </c>
       <c r="B315" t="n">
-        <v>-0.9279394482883139</v>
+        <v>-0.9466589205079275</v>
       </c>
       <c r="C315" t="n">
-        <v>0.1314508553617306</v>
+        <v>0.1053591485320955</v>
       </c>
       <c r="D315" t="b">
         <v>0</v>
@@ -10848,10 +10848,10 @@
         <v>45747</v>
       </c>
       <c r="B316" t="n">
-        <v>-0.8870883778336536</v>
+        <v>-0.9152014981959544</v>
       </c>
       <c r="C316" t="n">
-        <v>0.1564856013311842</v>
+        <v>0.08969259728684205</v>
       </c>
       <c r="D316" t="b">
         <v>0</v>
@@ -10871,6 +10871,39 @@
         </is>
       </c>
       <c r="I316" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B317" t="n">
+        <v>-0.8970238361805523</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.07001454885654049</v>
+      </c>
+      <c r="D317" t="b">
+        <v>0</v>
+      </c>
+      <c r="E317" t="b">
+        <v>1</v>
+      </c>
+      <c r="F317" t="n">
+        <v>-0.425986313602942</v>
+      </c>
+      <c r="G317" t="n">
+        <v>311338.4124816686</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
         <is>
           <t>Type 1</t>
         </is>
